--- a/data/trans_orig/IP22-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65410</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80173</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79131</t>
+          <t>79220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95154</t>
+          <t>95084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149508</t>
+          <t>149251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171847</t>
+          <t>172081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25624</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41679</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55107</t>
+          <t>54086</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76857</t>
+          <t>77402</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190731</t>
+          <t>191158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211588</t>
+          <t>212119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>172975</t>
+          <t>173175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196282</t>
+          <t>195211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371397</t>
+          <t>369801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402981</t>
+          <t>400654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61457</t>
+          <t>61363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>57472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79443</t>
+          <t>79378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102987</t>
+          <t>104744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135003</t>
+          <t>135212</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98589</t>
+          <t>98498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112433</t>
+          <t>111994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113816</t>
+          <t>113181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>127077</t>
+          <t>126490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216810</t>
+          <t>216127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236034</t>
+          <t>235559</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159285</t>
+          <t>158199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174854</t>
+          <t>174533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162292</t>
+          <t>162926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179736</t>
+          <t>180239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>327815</t>
+          <t>328502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>351377</t>
+          <t>351972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25090</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>41833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48048</t>
+          <t>47308</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71464</t>
+          <t>70758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>547412</t>
+          <t>547601</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582857</t>
+          <t>582686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1091840</t>
+          <t>1088057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1139182</t>
+          <t>1139560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114159</t>
+          <t>113439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147599</t>
+          <t>147250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137001</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172167</t>
+          <t>171199</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260816</t>
+          <t>259608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307581</t>
+          <t>310094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86701</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105550</t>
+          <t>105827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94797</t>
+          <t>95463</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112717</t>
+          <t>112880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186699</t>
+          <t>187207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212701</t>
+          <t>212133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>39749</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59062</t>
+          <t>58796</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>30953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49007</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75841</t>
+          <t>77571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101807</t>
+          <t>102317</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147165</t>
+          <t>148898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172178</t>
+          <t>172667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158363</t>
+          <t>157101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184937</t>
+          <t>185100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>314180</t>
+          <t>315441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349692</t>
+          <t>351342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61015</t>
+          <t>61056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>84526</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79515</t>
+          <t>79116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105983</t>
+          <t>106813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148447</t>
+          <t>148501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184697</t>
+          <t>183579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126784</t>
+          <t>126492</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141453</t>
+          <t>140931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121676</t>
+          <t>121792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138028</t>
+          <t>138462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>254489</t>
+          <t>253351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275472</t>
+          <t>276319</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29962</t>
+          <t>29767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38891</t>
+          <t>38559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>60124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144734</t>
+          <t>145207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158151</t>
+          <t>158788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>127084</t>
+          <t>126030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>144560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>275911</t>
+          <t>276149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299529</t>
+          <t>299303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31979</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72304</t>
+          <t>72282</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>521519</t>
+          <t>522517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>563002</t>
+          <t>563418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1056984</t>
+          <t>1057381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1114274</t>
+          <t>1112764</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183558</t>
+          <t>182195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181402</t>
+          <t>181662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222058</t>
+          <t>221723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336866</t>
+          <t>338655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393635</t>
+          <t>393261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94729</t>
+          <t>95192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109975</t>
+          <t>109809</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91446</t>
+          <t>92268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106566</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191201</t>
+          <t>192349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>214143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32086</t>
+          <t>30874</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40760</t>
+          <t>39170</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61726</t>
+          <t>60205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155650</t>
+          <t>155742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174289</t>
+          <t>174228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204766</t>
+          <t>205893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224861</t>
+          <t>224064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366851</t>
+          <t>367418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394108</t>
+          <t>394406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>33223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51224</t>
+          <t>50735</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32831</t>
+          <t>33588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>51838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70432</t>
+          <t>71218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97197</t>
+          <t>97703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149390</t>
+          <t>149401</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>165318</t>
+          <t>165847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148450</t>
+          <t>148633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165618</t>
+          <t>165776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>302967</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>326561</t>
+          <t>327078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38334</t>
+          <t>37292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48268</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71512</t>
+          <t>70792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144945</t>
+          <t>147222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159265</t>
+          <t>160387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136592</t>
+          <t>137812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>154191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>288940</t>
+          <t>287670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>309586</t>
+          <t>309449</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27680</t>
+          <t>25730</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36221</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35462</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55809</t>
+          <t>58481</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102190</t>
+          <t>101910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134076</t>
+          <t>131857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105714</t>
+          <t>105517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>138030</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216644</t>
+          <t>214536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262404</t>
+          <t>260543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36645</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>42002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>52960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83093</t>
+          <t>82850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97180</t>
+          <t>97644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>36105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127819</t>
+          <t>127253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142779</t>
+          <t>143511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140194</t>
+          <t>140948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159755</t>
+          <t>159249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>274915</t>
+          <t>275503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300110</t>
+          <t>298578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31480</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>23305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>41606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41743</t>
+          <t>43275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66938</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137983</t>
+          <t>138179</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>153716</t>
+          <t>154714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166356</t>
+          <t>166312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187089</t>
+          <t>188342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>311113</t>
+          <t>311527</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>336162</t>
+          <t>338107</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46134</t>
+          <t>46178</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48677</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73726</t>
+          <t>73312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>219481</t>
+          <t>216631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>248820</t>
+          <t>248085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254819</t>
+          <t>253532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>278398</t>
+          <t>277280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>482418</t>
+          <t>482199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>521241</t>
+          <t>520337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26638</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55977</t>
+          <t>58827</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59699</t>
+          <t>60603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98522</t>
+          <t>98741</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>540737</t>
+          <t>539979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>580162</t>
+          <t>580609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1175066</t>
+          <t>1174859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1230418</t>
+          <t>1232167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123880</t>
+          <t>124638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251523</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
